--- a/grille_extract_test.xlsx
+++ b/grille_extract_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodbere\Documents\GitHub\systematic_review_final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodbert-e\Documents\GitHub\systematic_review_final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB58726-1658-462A-B252-743C6C321974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CA0C6D-BD15-4E06-98E0-653BA7EF8D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26192" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4199" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4410" uniqueCount="1127">
   <si>
     <t>DiVincenzo_2018</t>
   </si>
@@ -4130,6 +4133,18 @@
   </si>
   <si>
     <t>Importance of considering the temporal aspect: detailed analysis of transfers (rather than their aggregation) reveals the mechanisms underlying the formation of social structures between organizations.</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>data_extractor</t>
+  </si>
+  <si>
+    <t>extraction_date</t>
+  </si>
+  <si>
+    <t>eligible</t>
   </si>
 </sst>
 </file>
@@ -4343,7 +4358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4432,6 +4447,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4691,12 +4707,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0A234209-000F-4083-8F59-7A4627BAD561}" name="Tableau1" displayName="Tableau1" ref="A1:AY105" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23">
-  <autoFilter ref="A1:AY105" xr:uid="{0A234209-000F-4083-8F59-7A4627BAD561}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AY105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0A234209-000F-4083-8F59-7A4627BAD561}" name="Tableau1" displayName="Tableau1" ref="A1:BB105" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23">
+  <autoFilter ref="A1:BB105" xr:uid="{0A234209-000F-4083-8F59-7A4627BAD561}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BB105">
     <sortCondition ref="A1:A105"/>
   </sortState>
-  <tableColumns count="51">
+  <tableColumns count="54">
     <tableColumn id="4" xr3:uid="{D96C3F57-F34A-42FA-AB0C-6543F924C192}" name="author_year"/>
     <tableColumn id="5" xr3:uid="{A3826C7A-C40B-4688-B0E4-0DC1E0346645}" name="title" dataDxfId="21"/>
     <tableColumn id="6" xr3:uid="{5FA18405-7C60-4EBE-82B7-83D3B5FA6B96}" name="authors"/>
@@ -4744,6 +4760,9 @@
     <tableColumn id="9" xr3:uid="{FD325BB2-E87B-4F33-B21E-26F585C5728C}" name="prop_model_interv_grp"/>
     <tableColumn id="45" xr3:uid="{D7150D92-3FD4-4546-B36F-7B8581F7B3A9}" name="epidemio_data_yes_no"/>
     <tableColumn id="21" xr3:uid="{5753AFB9-92FC-40CA-9FA0-7C856A5EC371}" name="epidemio_data_categ"/>
+    <tableColumn id="3" xr3:uid="{DE189695-F9BD-4DDE-A527-07E7249A1BA8}" name="data_extractor"/>
+    <tableColumn id="15" xr3:uid="{EEDC4F57-F86B-4A2B-8AD3-850EF0772A02}" name="extraction_date"/>
+    <tableColumn id="16" xr3:uid="{AB0ED796-B6BD-4FC7-AEEB-CEB0403FE9E6}" name="eligible"/>
     <tableColumn id="47" xr3:uid="{7DC737CE-24F7-4F20-8D4D-A16EF3AB2CDE}" name="found_how"/>
     <tableColumn id="49" xr3:uid="{D999DCE2-AFC4-4A46-AF31-29DAB9E6F286}" name="Conclusion 1" dataDxfId="2"/>
     <tableColumn id="50" xr3:uid="{49A4F5A6-7A6A-4228-A59C-11CD952A1CAA}" name="Conclusion 2" dataDxfId="1"/>
@@ -5016,55 +5035,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CJ105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:CM105"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.109375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+    <col min="4" max="4" width="11.375" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="40.33203125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="31.33203125" style="13" customWidth="1"/>
-    <col min="9" max="12" width="31.33203125" style="6" customWidth="1"/>
-    <col min="13" max="13" width="31.33203125" style="14" customWidth="1"/>
-    <col min="14" max="14" width="44.21875" style="7" customWidth="1"/>
-    <col min="15" max="15" width="40.33203125" customWidth="1"/>
-    <col min="16" max="18" width="32.77734375" customWidth="1"/>
-    <col min="19" max="19" width="27.21875" style="18" customWidth="1"/>
-    <col min="20" max="20" width="27.21875" customWidth="1"/>
-    <col min="21" max="21" width="54.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="40.375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="31.375" style="13" customWidth="1"/>
+    <col min="9" max="12" width="31.375" style="6" customWidth="1"/>
+    <col min="13" max="13" width="31.375" style="14" customWidth="1"/>
+    <col min="14" max="14" width="44.25" style="7" customWidth="1"/>
+    <col min="15" max="15" width="40.375" customWidth="1"/>
+    <col min="16" max="18" width="32.75" customWidth="1"/>
+    <col min="19" max="19" width="27.25" style="18" customWidth="1"/>
+    <col min="20" max="20" width="27.25" customWidth="1"/>
+    <col min="21" max="21" width="54.625" customWidth="1"/>
     <col min="22" max="22" width="59" customWidth="1"/>
-    <col min="23" max="23" width="90.44140625" style="18" customWidth="1"/>
+    <col min="23" max="23" width="90.5" style="18" customWidth="1"/>
     <col min="24" max="24" width="31" customWidth="1"/>
-    <col min="25" max="25" width="26.44140625" style="15" customWidth="1"/>
-    <col min="26" max="26" width="26.44140625" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" customWidth="1"/>
+    <col min="25" max="25" width="26.5" style="15" customWidth="1"/>
+    <col min="26" max="26" width="26.5" customWidth="1"/>
+    <col min="27" max="27" width="41.25" customWidth="1"/>
     <col min="28" max="28" width="31" customWidth="1"/>
-    <col min="29" max="29" width="42.33203125" customWidth="1"/>
-    <col min="30" max="30" width="31.44140625" customWidth="1"/>
-    <col min="31" max="32" width="30.88671875" customWidth="1"/>
-    <col min="33" max="33" width="59.21875" style="9" customWidth="1"/>
-    <col min="34" max="34" width="41.109375" style="10" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="28.88671875" style="9" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="58.44140625" style="6" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="44.88671875" customWidth="1"/>
-    <col min="38" max="38" width="44.88671875" style="9" customWidth="1"/>
+    <col min="29" max="29" width="42.375" customWidth="1"/>
+    <col min="30" max="30" width="31.5" customWidth="1"/>
+    <col min="31" max="32" width="30.875" customWidth="1"/>
+    <col min="33" max="33" width="59.25" style="9" customWidth="1"/>
+    <col min="34" max="34" width="41.125" style="10" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="28.875" style="9" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="58.5" style="6" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="44.875" customWidth="1"/>
+    <col min="38" max="38" width="44.875" style="9" customWidth="1"/>
     <col min="39" max="39" width="28" style="10" customWidth="1"/>
-    <col min="40" max="40" width="20.44140625" customWidth="1"/>
-    <col min="41" max="41" width="22.21875" customWidth="1"/>
-    <col min="42" max="42" width="31.109375" customWidth="1"/>
+    <col min="40" max="40" width="20.5" customWidth="1"/>
+    <col min="41" max="41" width="22.25" customWidth="1"/>
+    <col min="42" max="42" width="31.125" customWidth="1"/>
     <col min="43" max="43" width="43" style="6" customWidth="1"/>
-    <col min="44" max="44" width="18.88671875" style="6" customWidth="1"/>
-    <col min="45" max="45" width="36.77734375" customWidth="1"/>
-    <col min="46" max="47" width="22.88671875" style="23" customWidth="1"/>
-    <col min="48" max="48" width="44.44140625" style="17" customWidth="1"/>
-    <col min="49" max="50" width="17.109375" customWidth="1"/>
-    <col min="51" max="51" width="26.44140625" customWidth="1"/>
+    <col min="44" max="44" width="18.875" style="6" customWidth="1"/>
+    <col min="45" max="45" width="36.75" customWidth="1"/>
+    <col min="46" max="50" width="22.875" style="23" customWidth="1"/>
+    <col min="51" max="51" width="44.5" style="17" customWidth="1"/>
+    <col min="52" max="53" width="17.125" customWidth="1"/>
+    <col min="54" max="54" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:88" s="3" customFormat="1" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:91" s="3" customFormat="1" ht="51.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>873</v>
       </c>
@@ -5206,20 +5225,29 @@
       <c r="AU1" s="34" t="s">
         <v>991</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AV1" s="34" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AW1" s="34" t="s">
+        <v>1125</v>
+      </c>
+      <c r="AX1" s="34" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AY1" s="3" t="s">
         <v>916</v>
       </c>
-      <c r="AW1" s="37" t="s">
+      <c r="AZ1" s="37" t="s">
         <v>1060</v>
       </c>
-      <c r="AX1" s="37" t="s">
+      <c r="BA1" s="37" t="s">
         <v>1061</v>
       </c>
-      <c r="AY1" s="37" t="s">
+      <c r="BB1" s="37" t="s">
         <v>1062</v>
       </c>
     </row>
-    <row r="2" spans="1:88" ht="39.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:91" ht="39.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>860</v>
       </c>
@@ -5350,19 +5378,28 @@
       </c>
       <c r="AU2"/>
       <c r="AV2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW2" s="40">
+        <v>45783</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY2" t="s">
         <v>1049</v>
       </c>
-      <c r="AW2" s="38" t="s">
+      <c r="AZ2" s="38" t="s">
         <v>1070</v>
       </c>
-      <c r="AX2" s="38" t="s">
+      <c r="BA2" s="38" t="s">
         <v>1071</v>
       </c>
-      <c r="AY2" s="38" t="s">
+      <c r="BB2" s="38" t="s">
         <v>1072</v>
       </c>
     </row>
-    <row r="3" spans="1:88" s="15" customFormat="1" ht="84.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:91" s="15" customFormat="1" ht="84.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1033</v>
       </c>
@@ -5495,14 +5532,20 @@
         <v>11</v>
       </c>
       <c r="AV3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW3" s="40">
+        <v>45944</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY3" t="s">
         <v>1050</v>
       </c>
-      <c r="AW3" s="21"/>
-      <c r="AX3" s="21"/>
-      <c r="AY3" s="21"/>
-      <c r="AZ3"/>
-      <c r="BA3"/>
-      <c r="BB3"/>
+      <c r="AZ3" s="21"/>
+      <c r="BA3" s="21"/>
+      <c r="BB3" s="21"/>
       <c r="BC3"/>
       <c r="BD3"/>
       <c r="BE3"/>
@@ -5537,8 +5580,11 @@
       <c r="CH3"/>
       <c r="CI3"/>
       <c r="CJ3"/>
+      <c r="CK3"/>
+      <c r="CL3"/>
+      <c r="CM3"/>
     </row>
-    <row r="4" spans="1:88" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:91" s="15" customFormat="1" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1034</v>
       </c>
@@ -5671,14 +5717,20 @@
         <v>11</v>
       </c>
       <c r="AV4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW4" s="40">
+        <v>45944</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY4" t="s">
         <v>1050</v>
       </c>
-      <c r="AW4" s="21"/>
-      <c r="AX4" s="21"/>
-      <c r="AY4" s="21"/>
-      <c r="AZ4"/>
-      <c r="BA4"/>
-      <c r="BB4"/>
+      <c r="AZ4" s="21"/>
+      <c r="BA4" s="21"/>
+      <c r="BB4" s="21"/>
       <c r="BC4"/>
       <c r="BD4"/>
       <c r="BE4"/>
@@ -5713,8 +5765,11 @@
       <c r="CH4"/>
       <c r="CI4"/>
       <c r="CJ4"/>
+      <c r="CK4"/>
+      <c r="CL4"/>
+      <c r="CM4"/>
     </row>
-    <row r="5" spans="1:88" s="15" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:91" s="15" customFormat="1" ht="156.9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>558</v>
       </c>
@@ -5851,20 +5906,26 @@
       </c>
       <c r="AU5"/>
       <c r="AV5" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW5" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY5" t="s">
         <v>1049</v>
       </c>
-      <c r="AW5" s="12" t="s">
+      <c r="AZ5" s="12" t="s">
         <v>1063</v>
       </c>
-      <c r="AX5" s="12" t="s">
+      <c r="BA5" s="12" t="s">
         <v>569</v>
       </c>
-      <c r="AY5" s="12" t="s">
+      <c r="BB5" s="12" t="s">
         <v>1065</v>
       </c>
-      <c r="AZ5"/>
-      <c r="BA5"/>
-      <c r="BB5"/>
       <c r="BC5"/>
       <c r="BD5"/>
       <c r="BE5"/>
@@ -5899,8 +5960,11 @@
       <c r="CH5"/>
       <c r="CI5"/>
       <c r="CJ5"/>
+      <c r="CK5"/>
+      <c r="CL5"/>
+      <c r="CM5"/>
     </row>
-    <row r="6" spans="1:88" s="15" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:91" s="15" customFormat="1" ht="99.85" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>796</v>
       </c>
@@ -6031,16 +6095,22 @@
       </c>
       <c r="AU6"/>
       <c r="AV6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW6" s="40">
+        <v>45782</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY6" t="s">
         <v>1049</v>
       </c>
-      <c r="AW6" s="12" t="s">
+      <c r="AZ6" s="12" t="s">
         <v>1064</v>
       </c>
-      <c r="AX6" s="12"/>
-      <c r="AY6" s="12"/>
-      <c r="AZ6"/>
-      <c r="BA6"/>
-      <c r="BB6"/>
+      <c r="BA6" s="12"/>
+      <c r="BB6" s="12"/>
       <c r="BC6"/>
       <c r="BD6"/>
       <c r="BE6"/>
@@ -6075,8 +6145,11 @@
       <c r="CH6"/>
       <c r="CI6"/>
       <c r="CJ6"/>
+      <c r="CK6"/>
+      <c r="CL6"/>
+      <c r="CM6"/>
     </row>
-    <row r="7" spans="1:88" s="15" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:91" s="15" customFormat="1" ht="128.4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>628</v>
       </c>
@@ -6209,20 +6282,26 @@
       </c>
       <c r="AU7"/>
       <c r="AV7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW7" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY7" t="s">
         <v>1049</v>
       </c>
-      <c r="AW7" s="39" t="s">
+      <c r="AZ7" s="39" t="s">
         <v>637</v>
       </c>
-      <c r="AX7" s="39" t="s">
+      <c r="BA7" s="39" t="s">
         <v>638</v>
       </c>
-      <c r="AY7" s="39" t="s">
+      <c r="BB7" s="39" t="s">
         <v>1073</v>
       </c>
-      <c r="AZ7"/>
-      <c r="BA7"/>
-      <c r="BB7"/>
       <c r="BC7"/>
       <c r="BD7"/>
       <c r="BE7"/>
@@ -6257,8 +6336,11 @@
       <c r="CH7"/>
       <c r="CI7"/>
       <c r="CJ7"/>
+      <c r="CK7"/>
+      <c r="CL7"/>
+      <c r="CM7"/>
     </row>
-    <row r="8" spans="1:88" s="15" customFormat="1" ht="103.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:91" s="15" customFormat="1" ht="103.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>453</v>
       </c>
@@ -6393,14 +6475,20 @@
       </c>
       <c r="AU8"/>
       <c r="AV8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW8" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY8" t="s">
         <v>1049</v>
       </c>
-      <c r="AW8" s="12"/>
-      <c r="AX8" s="12"/>
-      <c r="AY8" s="12"/>
-      <c r="AZ8"/>
-      <c r="BA8"/>
-      <c r="BB8"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
       <c r="BC8"/>
       <c r="BD8"/>
       <c r="BE8"/>
@@ -6435,8 +6523,11 @@
       <c r="CH8"/>
       <c r="CI8"/>
       <c r="CJ8"/>
+      <c r="CK8"/>
+      <c r="CL8"/>
+      <c r="CM8"/>
     </row>
-    <row r="9" spans="1:88" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:91" ht="104.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>464</v>
       </c>
@@ -6577,19 +6668,28 @@
       </c>
       <c r="AU9"/>
       <c r="AV9" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW9" s="40">
+        <v>45726</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW9" s="39" t="s">
+      <c r="AZ9" s="39" t="s">
         <v>1074</v>
       </c>
-      <c r="AX9" s="39" t="s">
+      <c r="BA9" s="39" t="s">
         <v>1075</v>
       </c>
-      <c r="AY9" s="39" t="s">
+      <c r="BB9" s="39" t="s">
         <v>1076</v>
       </c>
     </row>
-    <row r="10" spans="1:88" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:91" ht="199.7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>480</v>
       </c>
@@ -6730,19 +6830,28 @@
       </c>
       <c r="AU10"/>
       <c r="AV10" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW10" s="40">
+        <v>45726</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY10" t="s">
         <v>492</v>
       </c>
-      <c r="AW10" s="35" t="s">
+      <c r="AZ10" s="35" t="s">
         <v>493</v>
       </c>
-      <c r="AX10" s="39" t="s">
+      <c r="BA10" s="39" t="s">
         <v>1077</v>
       </c>
-      <c r="AY10" s="39" t="s">
+      <c r="BB10" s="39" t="s">
         <v>1078</v>
       </c>
     </row>
-    <row r="11" spans="1:88" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:91" ht="71.349999999999994" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>157</v>
       </c>
@@ -6876,19 +6985,28 @@
       </c>
       <c r="AU11"/>
       <c r="AV11" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW11" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY11" t="s">
         <v>1049</v>
       </c>
-      <c r="AW11" s="38" t="s">
+      <c r="AZ11" s="38" t="s">
         <v>1066</v>
       </c>
-      <c r="AX11" s="38" t="s">
+      <c r="BA11" s="38" t="s">
         <v>1067</v>
       </c>
-      <c r="AY11" s="38" t="s">
+      <c r="BB11" s="38" t="s">
         <v>1068</v>
       </c>
     </row>
-    <row r="12" spans="1:88" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:91" ht="57.1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>926</v>
       </c>
@@ -6999,13 +7117,20 @@
       </c>
       <c r="AU12"/>
       <c r="AV12" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW12"/>
+      <c r="AX12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY12" t="s">
         <v>1049</v>
       </c>
-      <c r="AW12" s="12"/>
-      <c r="AX12" s="12"/>
-      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
     </row>
-    <row r="13" spans="1:88" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:91" ht="57.1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>927</v>
       </c>
@@ -7116,13 +7241,20 @@
       </c>
       <c r="AU13"/>
       <c r="AV13" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW13"/>
+      <c r="AX13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY13" t="s">
         <v>1049</v>
       </c>
-      <c r="AW13" s="12"/>
-      <c r="AX13" s="12"/>
-      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
     </row>
-    <row r="14" spans="1:88" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:91" ht="57.1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>437</v>
       </c>
@@ -7258,19 +7390,28 @@
       </c>
       <c r="AU14"/>
       <c r="AV14" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW14" s="40">
+        <v>45726</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY14" t="s">
         <v>1049</v>
       </c>
-      <c r="AW14" s="12" t="s">
+      <c r="AZ14" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="AX14" s="12" t="s">
+      <c r="BA14" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="AY14" s="12" t="s">
+      <c r="BB14" s="12" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="15" spans="1:88" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:91" ht="85.6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>108</v>
       </c>
@@ -7409,19 +7550,28 @@
       </c>
       <c r="AU15"/>
       <c r="AV15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW15" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY15" t="s">
         <v>1049</v>
       </c>
-      <c r="AW15" s="12" t="s">
+      <c r="AZ15" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="AX15" s="12" t="s">
+      <c r="BA15" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="AY15" s="12" t="s">
+      <c r="BB15" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:88" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:91" ht="85.6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>580</v>
       </c>
@@ -7545,19 +7695,28 @@
       </c>
       <c r="AU16"/>
       <c r="AV16" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW16" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY16" t="s">
         <v>1049</v>
       </c>
-      <c r="AW16" s="12">
+      <c r="AZ16" s="12">
         <v>0</v>
       </c>
-      <c r="AX16" s="12">
+      <c r="BA16" s="12">
         <v>0</v>
       </c>
-      <c r="AY16" s="12">
+      <c r="BB16" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:51" ht="144" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" ht="142.65" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>412</v>
       </c>
@@ -7693,19 +7852,28 @@
       </c>
       <c r="AU17"/>
       <c r="AV17" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW17" s="40">
+        <v>45726</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY17" t="s">
         <v>1049</v>
       </c>
-      <c r="AW17" s="38" t="s">
+      <c r="AZ17" s="38" t="s">
         <v>422</v>
       </c>
-      <c r="AX17" s="38" t="s">
+      <c r="BA17" s="38" t="s">
         <v>423</v>
       </c>
-      <c r="AY17" s="38" t="s">
+      <c r="BB17" s="38" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="18" spans="1:51" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>639</v>
       </c>
@@ -7844,19 +8012,28 @@
       </c>
       <c r="AU18"/>
       <c r="AV18" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW18" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY18" t="s">
         <v>1049</v>
       </c>
-      <c r="AW18" s="12" t="s">
+      <c r="AZ18" s="12" t="s">
         <v>646</v>
       </c>
-      <c r="AX18" s="12" t="s">
+      <c r="BA18" s="12" t="s">
         <v>647</v>
       </c>
-      <c r="AY18" s="12">
+      <c r="BB18" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:51" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" ht="99.85" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>361</v>
       </c>
@@ -7995,19 +8172,28 @@
       </c>
       <c r="AU19"/>
       <c r="AV19" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW19" s="40">
+        <v>45725</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY19" t="s">
         <v>1049</v>
       </c>
-      <c r="AW19" s="12" t="s">
+      <c r="AZ19" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="AX19" s="12" t="s">
+      <c r="BA19" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="AY19" s="12" t="s">
+      <c r="BB19" s="12" t="s">
         <v>1069</v>
       </c>
     </row>
-    <row r="20" spans="1:51" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" ht="199.7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>309</v>
       </c>
@@ -8143,19 +8329,28 @@
       </c>
       <c r="AU20"/>
       <c r="AV20" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW20" s="40">
+        <v>45721</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY20" t="s">
         <v>1049</v>
       </c>
-      <c r="AW20" s="35" t="s">
+      <c r="AZ20" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="AX20" s="35" t="s">
+      <c r="BA20" s="35" t="s">
         <v>323</v>
       </c>
-      <c r="AY20" s="35" t="s">
+      <c r="BB20" s="35" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="21" spans="1:51" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" ht="199.7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>932</v>
       </c>
@@ -8270,12 +8465,19 @@
         <v>18</v>
       </c>
       <c r="AU21"/>
-      <c r="AV21"/>
-      <c r="AW21" s="35"/>
-      <c r="AX21" s="35"/>
-      <c r="AY21" s="35"/>
+      <c r="AV21" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW21"/>
+      <c r="AX21" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY21"/>
+      <c r="AZ21" s="35"/>
+      <c r="BA21" s="35"/>
+      <c r="BB21" s="35"/>
     </row>
-    <row r="22" spans="1:51" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>933</v>
       </c>
@@ -8390,12 +8592,19 @@
         <v>18</v>
       </c>
       <c r="AU22"/>
-      <c r="AV22"/>
-      <c r="AW22" s="35"/>
-      <c r="AX22" s="35"/>
-      <c r="AY22" s="35"/>
+      <c r="AV22" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW22"/>
+      <c r="AX22" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY22"/>
+      <c r="AZ22" s="35"/>
+      <c r="BA22" s="35"/>
+      <c r="BB22" s="35"/>
     </row>
-    <row r="23" spans="1:51" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>588</v>
       </c>
@@ -8524,19 +8733,28 @@
       </c>
       <c r="AU23"/>
       <c r="AV23" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW23" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY23" t="s">
         <v>1049</v>
       </c>
-      <c r="AW23" s="12" t="s">
+      <c r="AZ23" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="AX23" s="12" t="s">
+      <c r="BA23" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="AY23" s="12" t="s">
+      <c r="BB23" s="12" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="1:51" ht="202.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:54" ht="202.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>325</v>
       </c>
@@ -8675,19 +8893,28 @@
       </c>
       <c r="AU24"/>
       <c r="AV24" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW24" s="40">
+        <v>45721</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY24" t="s">
         <v>1049</v>
       </c>
-      <c r="AW24" s="12" t="s">
+      <c r="AZ24" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="AX24" s="12" t="s">
+      <c r="BA24" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="AY24" s="12" t="s">
+      <c r="BB24" s="12" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="25" spans="1:51" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>601</v>
       </c>
@@ -8816,19 +9043,28 @@
       </c>
       <c r="AU25"/>
       <c r="AV25" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW25" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY25" t="s">
         <v>1049</v>
       </c>
-      <c r="AW25" s="12" t="s">
+      <c r="AZ25" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="AX25" s="12" t="s">
+      <c r="BA25" s="12" t="s">
         <v>613</v>
       </c>
-      <c r="AY25" s="12" t="s">
+      <c r="BB25" s="12" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" ht="185.45" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -8964,19 +9200,28 @@
       </c>
       <c r="AU26"/>
       <c r="AV26" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW26" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY26" t="s">
         <v>1049</v>
       </c>
-      <c r="AW26" s="12" t="s">
+      <c r="AZ26" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="AX26" s="12" t="s">
+      <c r="BA26" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AY26" s="12" t="s">
+      <c r="BB26" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:51" ht="165" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" ht="129.1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>538</v>
       </c>
@@ -9114,17 +9359,26 @@
       </c>
       <c r="AU27"/>
       <c r="AV27" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW27" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX27" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY27" t="s">
         <v>1049</v>
       </c>
-      <c r="AW27" s="35" t="s">
+      <c r="AZ27" s="35" t="s">
         <v>547</v>
       </c>
-      <c r="AX27" s="35" t="s">
+      <c r="BA27" s="35" t="s">
         <v>548</v>
       </c>
-      <c r="AY27" s="36"/>
+      <c r="BB27" s="36"/>
     </row>
-    <row r="28" spans="1:51" ht="165" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" ht="142" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>253</v>
       </c>
@@ -9263,19 +9517,28 @@
       </c>
       <c r="AU28"/>
       <c r="AV28" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW28" s="40">
+        <v>45756</v>
+      </c>
+      <c r="AX28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY28" t="s">
         <v>1049</v>
       </c>
-      <c r="AW28" s="35" t="s">
+      <c r="AZ28" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="AX28" s="35" t="s">
+      <c r="BA28" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="AY28" s="35" t="s">
+      <c r="BB28" s="35" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="29" spans="1:51" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" ht="115.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>267</v>
       </c>
@@ -9414,19 +9677,28 @@
       </c>
       <c r="AU29"/>
       <c r="AV29" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW29" s="40">
+        <v>45721</v>
+      </c>
+      <c r="AX29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY29" t="s">
         <v>1049</v>
       </c>
-      <c r="AW29" s="35" t="s">
+      <c r="AZ29" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="AX29" s="36" t="s">
+      <c r="BA29" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="AY29" s="35" t="s">
+      <c r="BB29" s="35" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="30" spans="1:51" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" ht="99.85" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>279</v>
       </c>
@@ -9565,17 +9837,26 @@
       </c>
       <c r="AU30"/>
       <c r="AV30" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW30" s="40">
+        <v>45721</v>
+      </c>
+      <c r="AX30" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY30" t="s">
         <v>1049</v>
       </c>
-      <c r="AW30" s="22" t="s">
+      <c r="AZ30" s="22" t="s">
         <v>287</v>
       </c>
-      <c r="AX30" s="22" t="s">
+      <c r="BA30" s="22" t="s">
         <v>288</v>
       </c>
-      <c r="AY30" s="12"/>
+      <c r="BB30" s="12"/>
     </row>
-    <row r="31" spans="1:51" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>807</v>
       </c>
@@ -9714,19 +9995,28 @@
       </c>
       <c r="AU31"/>
       <c r="AV31" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW31" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX31" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY31" t="s">
         <v>1049</v>
       </c>
-      <c r="AW31" s="12" t="s">
+      <c r="AZ31" s="12" t="s">
         <v>815</v>
       </c>
-      <c r="AX31" s="12" t="s">
+      <c r="BA31" s="12" t="s">
         <v>816</v>
       </c>
-      <c r="AY31" s="12" t="s">
+      <c r="BB31" s="12" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="32" spans="1:51" ht="135" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" ht="103.25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>289</v>
       </c>
@@ -9865,19 +10155,28 @@
       </c>
       <c r="AU32"/>
       <c r="AV32" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW32" s="40">
+        <v>45721</v>
+      </c>
+      <c r="AX32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY32" t="s">
         <v>1057</v>
       </c>
-      <c r="AW32" s="35" t="s">
+      <c r="AZ32" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="AX32" s="35" t="s">
+      <c r="BA32" s="35" t="s">
         <v>1038</v>
       </c>
-      <c r="AY32" s="35" t="s">
+      <c r="BB32" s="35" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="33" spans="1:51" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>299</v>
       </c>
@@ -10016,19 +10315,28 @@
       </c>
       <c r="AU33"/>
       <c r="AV33" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW33" s="40">
+        <v>45721</v>
+      </c>
+      <c r="AX33" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY33" t="s">
         <v>1049</v>
       </c>
-      <c r="AW33" s="12" t="s">
+      <c r="AZ33" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="AX33" s="12" t="s">
+      <c r="BA33" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="AY33" s="12" t="s">
+      <c r="BB33" s="12" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="34" spans="1:51" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" ht="99.85" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>1000</v>
       </c>
@@ -10150,13 +10458,22 @@
         <v>11</v>
       </c>
       <c r="AV34" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW34" s="40">
+        <v>45944</v>
+      </c>
+      <c r="AX34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY34" t="s">
         <v>1050</v>
       </c>
-      <c r="AW34" s="36"/>
-      <c r="AX34" s="36"/>
-      <c r="AY34" s="36"/>
+      <c r="AZ34" s="36"/>
+      <c r="BA34" s="36"/>
+      <c r="BB34" s="36"/>
     </row>
-    <row r="35" spans="1:51" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>96</v>
       </c>
@@ -10294,19 +10611,28 @@
       </c>
       <c r="AU35"/>
       <c r="AV35" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW35" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX35" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY35" t="s">
         <v>1049</v>
       </c>
-      <c r="AW35" s="12" t="s">
+      <c r="AZ35" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AX35" s="12" t="s">
+      <c r="BA35" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY35" s="12" t="s">
+      <c r="BB35" s="12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:51" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" ht="114.15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>845</v>
       </c>
@@ -10442,19 +10768,28 @@
       </c>
       <c r="AU36"/>
       <c r="AV36" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW36" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX36" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY36" t="s">
         <v>1049</v>
       </c>
-      <c r="AW36" s="12" t="s">
+      <c r="AZ36" s="12" t="s">
         <v>857</v>
       </c>
-      <c r="AX36" s="12" t="s">
+      <c r="BA36" s="12" t="s">
         <v>858</v>
       </c>
-      <c r="AY36" s="12" t="s">
+      <c r="BB36" s="12" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="37" spans="1:51" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" ht="114.15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>209</v>
       </c>
@@ -10593,19 +10928,28 @@
       </c>
       <c r="AU37"/>
       <c r="AV37" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW37" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX37" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY37" t="s">
         <v>1049</v>
       </c>
-      <c r="AW37" s="12" t="s">
+      <c r="AZ37" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="AX37" s="12" t="s">
+      <c r="BA37" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="AY37" s="12" t="s">
+      <c r="BB37" s="12" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="38" spans="1:51" ht="72" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>648</v>
       </c>
@@ -10744,19 +11088,28 @@
       </c>
       <c r="AU38"/>
       <c r="AV38" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW38" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX38" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY38" t="s">
         <v>1049</v>
       </c>
-      <c r="AW38" s="12" t="s">
+      <c r="AZ38" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="AX38" s="12" t="s">
+      <c r="BA38" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="AY38" s="12" t="s">
+      <c r="BB38" s="12" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="39" spans="1:51" ht="165" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" ht="142" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>170</v>
       </c>
@@ -10892,19 +11245,28 @@
       </c>
       <c r="AU39"/>
       <c r="AV39" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW39" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX39" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY39" t="s">
         <v>1049</v>
       </c>
-      <c r="AW39" s="35" t="s">
+      <c r="AZ39" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="AX39" s="35" t="s">
+      <c r="BA39" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="AY39" s="35" t="s">
+      <c r="BB39" s="35" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="40" spans="1:51" ht="100.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>928</v>
       </c>
@@ -11014,12 +11376,19 @@
         <v>18</v>
       </c>
       <c r="AU40"/>
-      <c r="AV40" s="9"/>
-      <c r="AW40" s="35"/>
-      <c r="AX40" s="35"/>
-      <c r="AY40" s="35"/>
+      <c r="AV40" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW40"/>
+      <c r="AX40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY40" s="9"/>
+      <c r="AZ40" s="35"/>
+      <c r="BA40" s="35"/>
+      <c r="BB40" s="35"/>
     </row>
-    <row r="41" spans="1:51" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>929</v>
       </c>
@@ -11129,12 +11498,19 @@
         <v>18</v>
       </c>
       <c r="AU41"/>
-      <c r="AV41"/>
-      <c r="AW41" s="35"/>
-      <c r="AX41" s="35"/>
-      <c r="AY41" s="35"/>
+      <c r="AV41" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW41"/>
+      <c r="AX41" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY41"/>
+      <c r="AZ41" s="35"/>
+      <c r="BA41" s="35"/>
+      <c r="BB41" s="35"/>
     </row>
-    <row r="42" spans="1:51" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" ht="73.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>930</v>
       </c>
@@ -11244,12 +11620,19 @@
         <v>18</v>
       </c>
       <c r="AU42"/>
-      <c r="AV42"/>
-      <c r="AW42" s="35"/>
-      <c r="AX42" s="35"/>
-      <c r="AY42" s="35"/>
+      <c r="AV42" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW42"/>
+      <c r="AX42" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY42"/>
+      <c r="AZ42" s="35"/>
+      <c r="BA42" s="35"/>
+      <c r="BB42" s="35"/>
     </row>
-    <row r="43" spans="1:51" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>657</v>
       </c>
@@ -11388,19 +11771,28 @@
       </c>
       <c r="AU43"/>
       <c r="AV43" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW43" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX43" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY43" t="s">
         <v>1049</v>
       </c>
-      <c r="AW43" s="12" t="s">
+      <c r="AZ43" s="12" t="s">
         <v>662</v>
       </c>
-      <c r="AX43" s="12" t="s">
+      <c r="BA43" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="AY43" s="12" t="s">
+      <c r="BB43" s="12" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="44" spans="1:51" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" ht="228.25" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -11538,19 +11930,28 @@
       </c>
       <c r="AU44"/>
       <c r="AV44" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW44" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY44" t="s">
         <v>1049</v>
       </c>
-      <c r="AW44" s="38" t="s">
+      <c r="AZ44" s="38" t="s">
         <v>1120</v>
       </c>
-      <c r="AX44" s="38" t="s">
+      <c r="BA44" s="38" t="s">
         <v>1121</v>
       </c>
-      <c r="AY44" s="38" t="s">
+      <c r="BB44" s="38" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="45" spans="1:51" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1008</v>
       </c>
@@ -11625,13 +12026,22 @@
       <c r="AM45" s="9"/>
       <c r="AN45" s="10"/>
       <c r="AV45" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW45" s="40">
+        <v>45937</v>
+      </c>
+      <c r="AX45" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY45" t="s">
         <v>1050</v>
       </c>
-      <c r="AW45" s="21"/>
-      <c r="AX45" s="21"/>
-      <c r="AY45" s="21"/>
+      <c r="AZ45" s="21"/>
+      <c r="BA45" s="21"/>
+      <c r="BB45" s="21"/>
     </row>
-    <row r="46" spans="1:51" ht="15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1011</v>
       </c>
@@ -11740,13 +12150,20 @@
         <v>11</v>
       </c>
       <c r="AV46" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW46"/>
+      <c r="AX46" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY46" t="s">
         <v>1050</v>
       </c>
-      <c r="AW46" s="21"/>
-      <c r="AX46" s="21"/>
-      <c r="AY46" s="21"/>
+      <c r="AZ46" s="21"/>
+      <c r="BA46" s="21"/>
+      <c r="BB46" s="21"/>
     </row>
-    <row r="47" spans="1:51" ht="15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1009</v>
       </c>
@@ -11855,13 +12272,20 @@
         <v>11</v>
       </c>
       <c r="AV47" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW47"/>
+      <c r="AX47" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY47" t="s">
         <v>1050</v>
       </c>
-      <c r="AW47" s="21"/>
-      <c r="AX47" s="21"/>
-      <c r="AY47" s="21"/>
+      <c r="AZ47" s="21"/>
+      <c r="BA47" s="21"/>
+      <c r="BB47" s="21"/>
     </row>
-    <row r="48" spans="1:51" ht="15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1010</v>
       </c>
@@ -11970,13 +12394,20 @@
         <v>11</v>
       </c>
       <c r="AV48" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW48"/>
+      <c r="AX48" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY48" t="s">
         <v>1050</v>
       </c>
-      <c r="AW48" s="21"/>
-      <c r="AX48" s="21"/>
-      <c r="AY48" s="21"/>
+      <c r="AZ48" s="21"/>
+      <c r="BA48" s="21"/>
+      <c r="BB48" s="21"/>
     </row>
-    <row r="49" spans="1:51" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>665</v>
       </c>
@@ -12110,19 +12541,28 @@
       </c>
       <c r="AU49"/>
       <c r="AV49" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW49" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX49" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY49" t="s">
         <v>1049</v>
       </c>
-      <c r="AW49" s="12" t="s">
+      <c r="AZ49" s="12" t="s">
         <v>674</v>
       </c>
-      <c r="AX49" s="12" t="s">
+      <c r="BA49" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="AY49" s="12" t="s">
+      <c r="BB49" s="12" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="50" spans="1:51" ht="135" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" ht="116.15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>677</v>
       </c>
@@ -12261,19 +12701,28 @@
       </c>
       <c r="AU50"/>
       <c r="AV50" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW50" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX50" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY50" t="s">
         <v>1049</v>
       </c>
-      <c r="AW50" s="35" t="s">
+      <c r="AZ50" s="35" t="s">
         <v>684</v>
       </c>
-      <c r="AX50" s="35" t="s">
+      <c r="BA50" s="35" t="s">
         <v>685</v>
       </c>
-      <c r="AY50" s="35" t="s">
+      <c r="BB50" s="35" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="51" spans="1:51" ht="72" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>687</v>
       </c>
@@ -12402,19 +12851,28 @@
       </c>
       <c r="AU51"/>
       <c r="AV51" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW51" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX51" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY51" t="s">
         <v>1049</v>
       </c>
-      <c r="AW51" s="12" t="s">
+      <c r="AZ51" s="12" t="s">
         <v>693</v>
       </c>
-      <c r="AX51" s="12" t="s">
+      <c r="BA51" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="AY51" s="12">
+      <c r="BB51" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:51" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" ht="114.15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>695</v>
       </c>
@@ -12555,19 +13013,28 @@
       </c>
       <c r="AU52"/>
       <c r="AV52" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW52" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX52" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY52" t="s">
         <v>1058</v>
       </c>
-      <c r="AW52" s="39" t="s">
+      <c r="AZ52" s="39" t="s">
         <v>1080</v>
       </c>
-      <c r="AX52" s="39" t="s">
+      <c r="BA52" s="39" t="s">
         <v>1081</v>
       </c>
-      <c r="AY52" s="39" t="s">
+      <c r="BB52" s="39" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="53" spans="1:51" ht="105" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:54" ht="90.35" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>704</v>
       </c>
@@ -12706,19 +13173,28 @@
       </c>
       <c r="AU53"/>
       <c r="AV53" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW53" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX53" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY53" t="s">
         <v>1049</v>
       </c>
-      <c r="AW53" s="35" t="s">
+      <c r="AZ53" s="35" t="s">
         <v>709</v>
       </c>
-      <c r="AX53" s="35" t="s">
+      <c r="BA53" s="35" t="s">
         <v>710</v>
       </c>
-      <c r="AY53" s="35" t="s">
+      <c r="BB53" s="35" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="54" spans="1:51" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" ht="156.9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>712</v>
       </c>
@@ -12857,19 +13333,28 @@
       </c>
       <c r="AU54"/>
       <c r="AV54" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW54" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX54" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY54" t="s">
         <v>1049</v>
       </c>
-      <c r="AW54" s="35" t="s">
+      <c r="AZ54" s="35" t="s">
         <v>721</v>
       </c>
-      <c r="AX54" s="39" t="s">
+      <c r="BA54" s="39" t="s">
         <v>1083</v>
       </c>
-      <c r="AY54" s="39" t="s">
+      <c r="BB54" s="39" t="s">
         <v>1084</v>
       </c>
     </row>
-    <row r="55" spans="1:51" ht="150" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:54" ht="129.1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>722</v>
       </c>
@@ -13001,19 +13486,28 @@
       </c>
       <c r="AU55"/>
       <c r="AV55" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW55" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX55" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY55" t="s">
         <v>1049</v>
       </c>
-      <c r="AW55" s="35" t="s">
+      <c r="AZ55" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="AX55" s="35" t="s">
+      <c r="BA55" s="35" t="s">
         <v>730</v>
       </c>
-      <c r="AY55" s="39" t="s">
+      <c r="BB55" s="39" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="56" spans="1:51" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:54" ht="185.45" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>732</v>
       </c>
@@ -13152,19 +13646,28 @@
       </c>
       <c r="AU56"/>
       <c r="AV56" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW56" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX56" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY56" t="s">
         <v>1052</v>
       </c>
-      <c r="AW56" s="39" t="s">
+      <c r="AZ56" s="39" t="s">
         <v>1085</v>
       </c>
-      <c r="AX56" s="39" t="s">
+      <c r="BA56" s="39" t="s">
         <v>1086</v>
       </c>
-      <c r="AY56" s="39" t="s">
+      <c r="BB56" s="39" t="s">
         <v>1087</v>
       </c>
     </row>
-    <row r="57" spans="1:51" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:54" ht="242.5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>739</v>
       </c>
@@ -13303,19 +13806,28 @@
       </c>
       <c r="AU57"/>
       <c r="AV57" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW57" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX57" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY57" t="s">
         <v>1053</v>
       </c>
-      <c r="AW57" s="35" t="s">
+      <c r="AZ57" s="35" t="s">
         <v>746</v>
       </c>
-      <c r="AX57" s="39" t="s">
+      <c r="BA57" s="39" t="s">
         <v>1088</v>
       </c>
-      <c r="AY57" s="35">
+      <c r="BB57" s="35">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:51" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:54" ht="99.85" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>424</v>
       </c>
@@ -13448,19 +13960,28 @@
       </c>
       <c r="AU58"/>
       <c r="AV58" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW58" s="40">
+        <v>45726</v>
+      </c>
+      <c r="AX58" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY58" t="s">
         <v>1054</v>
       </c>
-      <c r="AW58" s="38" t="s">
+      <c r="AZ58" s="38" t="s">
         <v>434</v>
       </c>
-      <c r="AX58" s="38" t="s">
+      <c r="BA58" s="38" t="s">
         <v>435</v>
       </c>
-      <c r="AY58" s="38" t="s">
+      <c r="BB58" s="38" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="59" spans="1:51" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -13591,19 +14112,28 @@
       </c>
       <c r="AU59"/>
       <c r="AV59" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW59" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX59" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY59" t="s">
         <v>1049</v>
       </c>
-      <c r="AW59" s="38" t="s">
+      <c r="AZ59" s="38" t="s">
         <v>1117</v>
       </c>
-      <c r="AX59" s="38" t="s">
+      <c r="BA59" s="38" t="s">
         <v>1118</v>
       </c>
-      <c r="AY59" s="38" t="s">
+      <c r="BB59" s="38" t="s">
         <v>1119</v>
       </c>
     </row>
-    <row r="60" spans="1:51" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:54" ht="133.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>765</v>
       </c>
@@ -13736,19 +14266,28 @@
       </c>
       <c r="AU60"/>
       <c r="AV60" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW60" s="40">
+        <v>45770</v>
+      </c>
+      <c r="AX60" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY60" t="s">
         <v>1049</v>
       </c>
-      <c r="AW60" s="12" t="s">
+      <c r="AZ60" s="12" t="s">
         <v>774</v>
       </c>
-      <c r="AX60" s="12" t="s">
+      <c r="BA60" s="12" t="s">
         <v>775</v>
       </c>
-      <c r="AY60" s="12">
+      <c r="BB60" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:51" ht="114.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:54" ht="114.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -13883,19 +14422,28 @@
       </c>
       <c r="AU61"/>
       <c r="AV61" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW61" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX61" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY61" t="s">
         <v>1059</v>
       </c>
-      <c r="AW61" s="38" t="s">
+      <c r="AZ61" s="38" t="s">
         <v>1114</v>
       </c>
-      <c r="AX61" s="38" t="s">
+      <c r="BA61" s="38" t="s">
         <v>1115</v>
       </c>
-      <c r="AY61" s="38" t="s">
+      <c r="BB61" s="38" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="62" spans="1:51" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -14028,19 +14576,28 @@
       </c>
       <c r="AU62"/>
       <c r="AV62" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW62" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX62" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY62" t="s">
         <v>1055</v>
       </c>
-      <c r="AW62" s="38" t="s">
+      <c r="AZ62" s="38" t="s">
         <v>1111</v>
       </c>
-      <c r="AX62" s="38" t="s">
+      <c r="BA62" s="38" t="s">
         <v>1112</v>
       </c>
-      <c r="AY62" s="38" t="s">
+      <c r="BB62" s="38" t="s">
         <v>1113</v>
       </c>
     </row>
-    <row r="63" spans="1:51" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -14172,20 +14729,29 @@
         <v>11</v>
       </c>
       <c r="AU63"/>
-      <c r="AV63" s="9" t="s">
+      <c r="AV63" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW63" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX63" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY63" s="9" t="s">
         <v>1055</v>
       </c>
-      <c r="AW63" s="38" t="s">
+      <c r="AZ63" s="38" t="s">
         <v>1108</v>
       </c>
-      <c r="AX63" s="38" t="s">
+      <c r="BA63" s="38" t="s">
         <v>1109</v>
       </c>
-      <c r="AY63" s="38" t="s">
+      <c r="BB63" s="38" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="64" spans="1:51" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -14319,20 +14885,29 @@
         <v>11</v>
       </c>
       <c r="AU64"/>
-      <c r="AV64" s="9" t="s">
+      <c r="AV64" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW64" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX64" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY64" s="9" t="s">
         <v>1055</v>
       </c>
-      <c r="AW64" s="38" t="s">
+      <c r="AZ64" s="38" t="s">
         <v>1105</v>
       </c>
-      <c r="AX64" s="38" t="s">
+      <c r="BA64" s="38" t="s">
         <v>1106</v>
       </c>
-      <c r="AY64" s="38" t="s">
+      <c r="BB64" s="38" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="65" spans="1:51" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:54" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>1026</v>
       </c>
@@ -14443,14 +15018,23 @@
       <c r="AU65" t="s">
         <v>11</v>
       </c>
-      <c r="AV65" s="9" t="s">
+      <c r="AV65" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW65" s="40">
+        <v>45944</v>
+      </c>
+      <c r="AX65" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY65" s="9" t="s">
         <v>1050</v>
       </c>
-      <c r="AW65" s="21"/>
-      <c r="AX65" s="21"/>
-      <c r="AY65" s="21"/>
+      <c r="AZ65" s="21"/>
+      <c r="BA65" s="21"/>
+      <c r="BB65" s="21"/>
     </row>
-    <row r="66" spans="1:51" ht="72" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>337</v>
       </c>
@@ -14578,20 +15162,29 @@
         <v>11</v>
       </c>
       <c r="AU66"/>
-      <c r="AV66" s="9" t="s">
+      <c r="AV66" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW66" s="40">
+        <v>45721</v>
+      </c>
+      <c r="AX66" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY66" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW66" s="38" t="s">
+      <c r="AZ66" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="AX66" s="38" t="s">
+      <c r="BA66" s="38" t="s">
         <v>347</v>
       </c>
-      <c r="AY66" s="38" t="s">
+      <c r="BB66" s="38" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="67" spans="1:51" ht="72" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>349</v>
       </c>
@@ -14723,20 +15316,29 @@
         <v>11</v>
       </c>
       <c r="AU67"/>
-      <c r="AV67" s="9" t="s">
+      <c r="AV67" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW67" s="40">
+        <v>45725</v>
+      </c>
+      <c r="AX67" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY67" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW67" s="12" t="s">
+      <c r="AZ67" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="AX67" s="12" t="s">
+      <c r="BA67" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="AY67" s="12" t="s">
+      <c r="BB67" s="12" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="68" spans="1:51" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1021</v>
       </c>
@@ -14866,14 +15468,23 @@
       <c r="AU68" t="s">
         <v>11</v>
       </c>
-      <c r="AV68" s="9" t="s">
+      <c r="AV68" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW68" s="40">
+        <v>45944</v>
+      </c>
+      <c r="AX68" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY68" s="9" t="s">
         <v>1050</v>
       </c>
-      <c r="AW68" s="21"/>
-      <c r="AX68" s="21"/>
-      <c r="AY68" s="21"/>
+      <c r="AZ68" s="21"/>
+      <c r="BA68" s="21"/>
+      <c r="BB68" s="21"/>
     </row>
-    <row r="69" spans="1:51" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:54" ht="142.65" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>237</v>
       </c>
@@ -15008,20 +15619,29 @@
         <v>35</v>
       </c>
       <c r="AU69"/>
-      <c r="AV69" s="9" t="s">
+      <c r="AV69" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW69" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX69" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY69" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW69" s="35" t="s">
+      <c r="AZ69" s="35" t="s">
         <v>252</v>
       </c>
-      <c r="AX69" s="35">
+      <c r="BA69" s="35">
         <v>0</v>
       </c>
-      <c r="AY69" s="35">
+      <c r="BB69" s="35">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:51" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:54" ht="99.85" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>222</v>
       </c>
@@ -15151,20 +15771,29 @@
         <v>11</v>
       </c>
       <c r="AU70"/>
-      <c r="AV70" s="9" t="s">
+      <c r="AV70" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW70" s="40">
+        <v>45715</v>
+      </c>
+      <c r="AX70" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY70" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW70" s="38" t="s">
+      <c r="AZ70" s="38" t="s">
         <v>1089</v>
       </c>
-      <c r="AX70" s="38" t="s">
+      <c r="BA70" s="38" t="s">
         <v>1090</v>
       </c>
-      <c r="AY70" s="38" t="s">
+      <c r="BB70" s="38" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="71" spans="1:51" ht="105" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:54" ht="90.35" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>504</v>
       </c>
@@ -15302,20 +15931,29 @@
         <v>18</v>
       </c>
       <c r="AU71"/>
-      <c r="AV71" s="9" t="s">
+      <c r="AV71" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW71" s="40">
+        <v>45726</v>
+      </c>
+      <c r="AX71" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY71" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW71" s="35" t="s">
+      <c r="AZ71" s="35" t="s">
         <v>521</v>
       </c>
-      <c r="AX71" s="35" t="s">
+      <c r="BA71" s="35" t="s">
         <v>522</v>
       </c>
-      <c r="AY71" s="35" t="s">
+      <c r="BB71" s="35" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="72" spans="1:51" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:54" ht="120.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>935</v>
       </c>
@@ -15430,14 +16068,21 @@
         <v>18</v>
       </c>
       <c r="AU72"/>
-      <c r="AV72" s="9" t="s">
+      <c r="AV72" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW72"/>
+      <c r="AX72" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY72" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW72" s="35"/>
-      <c r="AX72" s="35"/>
-      <c r="AY72" s="35"/>
+      <c r="AZ72" s="35"/>
+      <c r="BA72" s="35"/>
+      <c r="BB72" s="35"/>
     </row>
-    <row r="73" spans="1:51" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>936</v>
       </c>
@@ -15552,14 +16197,21 @@
         <v>18</v>
       </c>
       <c r="AU73"/>
-      <c r="AV73" s="9" t="s">
+      <c r="AV73" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW73"/>
+      <c r="AX73" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY73" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW73" s="35"/>
-      <c r="AX73" s="35"/>
-      <c r="AY73" s="35"/>
+      <c r="AZ73" s="35"/>
+      <c r="BA73" s="35"/>
+      <c r="BB73" s="35"/>
     </row>
-    <row r="74" spans="1:51" ht="135" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:54" ht="116.15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>494</v>
       </c>
@@ -15697,20 +16349,29 @@
         <v>18</v>
       </c>
       <c r="AU74"/>
-      <c r="AV74" s="9" t="s">
+      <c r="AV74" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW74" s="40">
+        <v>45726</v>
+      </c>
+      <c r="AX74" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY74" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW74" s="35" t="s">
+      <c r="AZ74" s="35" t="s">
         <v>501</v>
       </c>
-      <c r="AX74" s="35" t="s">
+      <c r="BA74" s="35" t="s">
         <v>502</v>
       </c>
-      <c r="AY74" s="35" t="s">
+      <c r="BB74" s="35" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="75" spans="1:51" ht="240" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:54" ht="193.6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>776</v>
       </c>
@@ -15845,20 +16506,29 @@
         <v>35</v>
       </c>
       <c r="AU75"/>
-      <c r="AV75" s="9" t="s">
+      <c r="AV75" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW75" s="40">
+        <v>45727</v>
+      </c>
+      <c r="AX75" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY75" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW75" s="35" t="s">
+      <c r="AZ75" s="35" t="s">
         <v>783</v>
       </c>
-      <c r="AX75" s="35" t="s">
+      <c r="BA75" s="35" t="s">
         <v>784</v>
       </c>
-      <c r="AY75" s="35">
+      <c r="BB75" s="35">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:51" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:54" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>615</v>
       </c>
@@ -15996,20 +16666,29 @@
         <v>11</v>
       </c>
       <c r="AU76"/>
-      <c r="AV76" s="9" t="s">
+      <c r="AV76" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW76" s="40">
+        <v>45770</v>
+      </c>
+      <c r="AX76" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY76" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW76" s="12" t="s">
+      <c r="AZ76" s="12" t="s">
         <v>625</v>
       </c>
-      <c r="AX76" s="12" t="s">
+      <c r="BA76" s="12" t="s">
         <v>626</v>
       </c>
-      <c r="AY76" s="12" t="s">
+      <c r="BB76" s="12" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="77" spans="1:51" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:54" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>938</v>
       </c>
@@ -16125,12 +16804,19 @@
         <v>11</v>
       </c>
       <c r="AU77"/>
-      <c r="AV77" s="9"/>
-      <c r="AW77" s="12"/>
-      <c r="AX77" s="12"/>
-      <c r="AY77" s="12"/>
+      <c r="AV77" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW77"/>
+      <c r="AX77" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY77" s="9"/>
+      <c r="AZ77" s="12"/>
+      <c r="BA77" s="12"/>
+      <c r="BB77" s="12"/>
     </row>
-    <row r="78" spans="1:51" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:54" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>937</v>
       </c>
@@ -16246,12 +16932,19 @@
         <v>11</v>
       </c>
       <c r="AU78"/>
-      <c r="AV78" s="9"/>
-      <c r="AW78" s="12"/>
-      <c r="AX78" s="12"/>
-      <c r="AY78" s="12"/>
+      <c r="AV78" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW78"/>
+      <c r="AX78" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY78" s="9"/>
+      <c r="AZ78" s="12"/>
+      <c r="BA78" s="12"/>
+      <c r="BB78" s="12"/>
     </row>
-    <row r="79" spans="1:51" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>387</v>
       </c>
@@ -16386,20 +17079,29 @@
         <v>11</v>
       </c>
       <c r="AU79"/>
-      <c r="AV79" s="9" t="s">
+      <c r="AV79" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW79" s="40">
+        <v>45722</v>
+      </c>
+      <c r="AX79" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY79" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW79" s="38" t="s">
+      <c r="AZ79" s="38" t="s">
         <v>398</v>
       </c>
-      <c r="AX79" s="38" t="s">
+      <c r="BA79" s="38" t="s">
         <v>399</v>
       </c>
-      <c r="AY79" s="38" t="s">
+      <c r="BB79" s="38" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="80" spans="1:51" ht="72" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>401</v>
       </c>
@@ -16534,20 +17236,29 @@
         <v>11</v>
       </c>
       <c r="AU80"/>
-      <c r="AV80" s="9" t="s">
+      <c r="AV80" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW80" s="40">
+        <v>45722</v>
+      </c>
+      <c r="AX80" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY80" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW80" s="38" t="s">
+      <c r="AZ80" s="38" t="s">
         <v>409</v>
       </c>
-      <c r="AX80" s="38" t="s">
+      <c r="BA80" s="38" t="s">
         <v>410</v>
       </c>
-      <c r="AY80" s="38" t="s">
+      <c r="BB80" s="38" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="81" spans="1:51" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>189</v>
       </c>
@@ -16676,20 +17387,29 @@
         <v>11</v>
       </c>
       <c r="AU81"/>
-      <c r="AV81" s="9" t="s">
+      <c r="AV81" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW81" s="40">
+        <v>45714</v>
+      </c>
+      <c r="AX81" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY81" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW81" s="12">
+      <c r="AZ81" s="12">
         <v>0</v>
       </c>
-      <c r="AX81" s="12">
+      <c r="BA81" s="12">
         <v>0</v>
       </c>
-      <c r="AY81" s="12">
+      <c r="BB81" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:51" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>199</v>
       </c>
@@ -16821,20 +17541,29 @@
         <v>11</v>
       </c>
       <c r="AU82"/>
-      <c r="AV82" s="9" t="s">
+      <c r="AV82" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW82" s="40">
+        <v>45714</v>
+      </c>
+      <c r="AX82" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY82" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW82" s="12">
+      <c r="AZ82" s="12">
         <v>0</v>
       </c>
-      <c r="AX82" s="12">
+      <c r="BA82" s="12">
         <v>0</v>
       </c>
-      <c r="AY82" s="12">
+      <c r="BB82" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:51" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:54" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>747</v>
       </c>
@@ -16967,20 +17696,29 @@
         <v>35</v>
       </c>
       <c r="AU83"/>
-      <c r="AV83" s="9" t="s">
+      <c r="AV83" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW83" s="40">
+        <v>45724</v>
+      </c>
+      <c r="AX83" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY83" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW83" s="39" t="s">
+      <c r="AZ83" s="39" t="s">
         <v>1092</v>
       </c>
-      <c r="AX83" s="39" t="s">
+      <c r="BA83" s="39" t="s">
         <v>1093</v>
       </c>
-      <c r="AY83" s="39" t="s">
+      <c r="BB83" s="39" t="s">
         <v>1094</v>
       </c>
     </row>
-    <row r="84" spans="1:51" ht="81.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:54" ht="81.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>570</v>
       </c>
@@ -17118,20 +17856,29 @@
         <v>11</v>
       </c>
       <c r="AU84"/>
-      <c r="AV84" s="9" t="s">
+      <c r="AV84" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW84" s="40">
+        <v>45723</v>
+      </c>
+      <c r="AX84" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY84" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW84" s="38" t="s">
+      <c r="AZ84" s="38" t="s">
         <v>1095</v>
       </c>
-      <c r="AX84" s="38" t="s">
+      <c r="BA84" s="38" t="s">
         <v>1096</v>
       </c>
-      <c r="AY84" s="38" t="s">
+      <c r="BB84" s="38" t="s">
         <v>1097</v>
       </c>
     </row>
-    <row r="85" spans="1:51" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:54" ht="156.9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>828</v>
       </c>
@@ -17262,20 +18009,29 @@
         <v>18</v>
       </c>
       <c r="AU85"/>
-      <c r="AV85" s="9" t="s">
+      <c r="AV85" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW85" s="40">
+        <v>45723</v>
+      </c>
+      <c r="AX85" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY85" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW85" s="35" t="s">
+      <c r="AZ85" s="35" t="s">
         <v>842</v>
       </c>
-      <c r="AX85" s="35" t="s">
+      <c r="BA85" s="35" t="s">
         <v>843</v>
       </c>
-      <c r="AY85" s="35" t="s">
+      <c r="BB85" s="35" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="86" spans="1:51" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>951</v>
       </c>
@@ -17389,12 +18145,19 @@
         <v>18</v>
       </c>
       <c r="AU86"/>
-      <c r="AV86" s="9"/>
-      <c r="AW86" s="35"/>
-      <c r="AX86" s="35"/>
-      <c r="AY86" s="35"/>
+      <c r="AV86" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW86"/>
+      <c r="AX86" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY86" s="9"/>
+      <c r="AZ86" s="35"/>
+      <c r="BA86" s="35"/>
+      <c r="BB86" s="35"/>
     </row>
-    <row r="87" spans="1:51" ht="159" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:54" ht="157.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>953</v>
       </c>
@@ -17508,12 +18271,19 @@
         <v>18</v>
       </c>
       <c r="AU87"/>
-      <c r="AV87" s="9"/>
-      <c r="AW87" s="35"/>
-      <c r="AX87" s="35"/>
-      <c r="AY87" s="35"/>
+      <c r="AV87" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW87"/>
+      <c r="AX87" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY87" s="9"/>
+      <c r="AZ87" s="35"/>
+      <c r="BA87" s="35"/>
+      <c r="BB87" s="35"/>
     </row>
-    <row r="88" spans="1:51" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:54" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>952</v>
       </c>
@@ -17629,12 +18399,19 @@
         <v>18</v>
       </c>
       <c r="AU88"/>
-      <c r="AV88" s="9"/>
-      <c r="AW88" s="35"/>
-      <c r="AX88" s="35"/>
-      <c r="AY88" s="35"/>
+      <c r="AV88" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW88"/>
+      <c r="AX88" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY88" s="9"/>
+      <c r="AZ88" s="35"/>
+      <c r="BA88" s="35"/>
+      <c r="BB88" s="35"/>
     </row>
-    <row r="89" spans="1:51" ht="150" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:54" ht="149.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>950</v>
       </c>
@@ -17748,12 +18525,19 @@
         <v>18</v>
       </c>
       <c r="AU89"/>
-      <c r="AV89" s="9"/>
-      <c r="AW89" s="35"/>
-      <c r="AX89" s="35"/>
-      <c r="AY89" s="35"/>
+      <c r="AV89" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW89"/>
+      <c r="AX89" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY89" s="9"/>
+      <c r="AZ89" s="35"/>
+      <c r="BA89" s="35"/>
+      <c r="BB89" s="35"/>
     </row>
-    <row r="90" spans="1:51" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>949</v>
       </c>
@@ -17867,12 +18651,19 @@
         <v>18</v>
       </c>
       <c r="AU90"/>
-      <c r="AV90" s="9"/>
-      <c r="AW90" s="35"/>
-      <c r="AX90" s="35"/>
-      <c r="AY90" s="35"/>
+      <c r="AV90" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW90"/>
+      <c r="AX90" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY90" s="9"/>
+      <c r="AZ90" s="35"/>
+      <c r="BA90" s="35"/>
+      <c r="BB90" s="35"/>
     </row>
-    <row r="91" spans="1:51" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>372</v>
       </c>
@@ -18010,20 +18801,29 @@
         <v>11</v>
       </c>
       <c r="AU91"/>
-      <c r="AV91" s="9" t="s">
+      <c r="AV91" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW91" s="40">
+        <v>45722</v>
+      </c>
+      <c r="AX91" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY91" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW91" s="38" t="s">
+      <c r="AZ91" s="38" t="s">
         <v>384</v>
       </c>
-      <c r="AX91" s="38" t="s">
+      <c r="BA91" s="38" t="s">
         <v>385</v>
       </c>
-      <c r="AY91" s="38" t="s">
+      <c r="BB91" s="38" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="92" spans="1:51" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>524</v>
       </c>
@@ -18158,20 +18958,29 @@
         <v>11</v>
       </c>
       <c r="AU92"/>
-      <c r="AV92" s="9" t="s">
+      <c r="AV92" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW92" s="40">
+        <v>45723</v>
+      </c>
+      <c r="AX92" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY92" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW92" s="12" t="s">
+      <c r="AZ92" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="AX92" s="12" t="s">
+      <c r="BA92" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="AY92" s="12" t="s">
+      <c r="BB92" s="12" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="93" spans="1:51" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>785</v>
       </c>
@@ -18306,20 +19115,29 @@
         <v>35</v>
       </c>
       <c r="AU93"/>
-      <c r="AV93" s="9" t="s">
+      <c r="AV93" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW93" s="40">
+        <v>45723</v>
+      </c>
+      <c r="AX93" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY93" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW93" s="35" t="s">
+      <c r="AZ93" s="35" t="s">
         <v>794</v>
       </c>
-      <c r="AX93" s="35" t="s">
+      <c r="BA93" s="35" t="s">
         <v>795</v>
       </c>
-      <c r="AY93" s="35">
+      <c r="BB93" s="35">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:51" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>549</v>
       </c>
@@ -18453,14 +19271,23 @@
         <v>18</v>
       </c>
       <c r="AU94"/>
-      <c r="AV94" s="9" t="s">
+      <c r="AV94" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW94" s="40">
+        <v>45723</v>
+      </c>
+      <c r="AX94" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY94" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW94" s="35"/>
-      <c r="AX94" s="35"/>
-      <c r="AY94" s="35"/>
+      <c r="AZ94" s="35"/>
+      <c r="BA94" s="35"/>
+      <c r="BB94" s="35"/>
     </row>
-    <row r="95" spans="1:51" ht="72.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:54" ht="72.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>755</v>
       </c>
@@ -18595,20 +19422,29 @@
         <v>11</v>
       </c>
       <c r="AU95"/>
-      <c r="AV95" s="9" t="s">
+      <c r="AV95" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW95" s="40">
+        <v>45728</v>
+      </c>
+      <c r="AX95" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY95" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW95" s="12" t="s">
+      <c r="AZ95" s="12" t="s">
         <v>763</v>
       </c>
-      <c r="AX95" s="12" t="s">
+      <c r="BA95" s="12" t="s">
         <v>764</v>
       </c>
-      <c r="AY95" s="38" t="s">
+      <c r="BB95" s="38" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="96" spans="1:51" ht="150" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:54" ht="129.1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>818</v>
       </c>
@@ -18740,20 +19576,29 @@
         <v>18</v>
       </c>
       <c r="AU96"/>
-      <c r="AV96" s="9" t="s">
+      <c r="AV96" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW96" s="40">
+        <v>45728</v>
+      </c>
+      <c r="AX96" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY96" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW96" s="35" t="s">
+      <c r="AZ96" s="35" t="s">
         <v>825</v>
       </c>
-      <c r="AX96" s="35" t="s">
+      <c r="BA96" s="35" t="s">
         <v>826</v>
       </c>
-      <c r="AY96" s="35" t="s">
+      <c r="BB96" s="35" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="97" spans="1:51" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:54" ht="35.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -18885,18 +19730,27 @@
         <v>11</v>
       </c>
       <c r="AU97"/>
-      <c r="AV97" s="9" t="s">
+      <c r="AV97" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW97" s="40">
+        <v>45728</v>
+      </c>
+      <c r="AX97" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY97" s="9" t="s">
         <v>1055</v>
       </c>
-      <c r="AW97" s="38" t="s">
+      <c r="AZ97" s="38" t="s">
         <v>1103</v>
       </c>
-      <c r="AX97" s="38" t="s">
+      <c r="BA97" s="38" t="s">
         <v>1104</v>
       </c>
-      <c r="AY97" s="21"/>
+      <c r="BB97" s="21"/>
     </row>
-    <row r="98" spans="1:51" ht="165" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:54" ht="142" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -19033,20 +19887,29 @@
         <v>18</v>
       </c>
       <c r="AU98"/>
-      <c r="AV98" s="9" t="s">
+      <c r="AV98" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW98" s="40">
+        <v>45728</v>
+      </c>
+      <c r="AX98" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY98" s="9" t="s">
         <v>1056</v>
       </c>
-      <c r="AW98" s="35" t="s">
+      <c r="AZ98" s="35" t="s">
         <v>1102</v>
       </c>
-      <c r="AX98" s="35" t="s">
+      <c r="BA98" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="AY98" s="35" t="s">
+      <c r="BB98" s="35" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="99" spans="1:51" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>921</v>
       </c>
@@ -19160,14 +20023,21 @@
         <v>18</v>
       </c>
       <c r="AU99"/>
-      <c r="AV99" s="9" t="s">
+      <c r="AV99" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW99"/>
+      <c r="AX99" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY99" s="9" t="s">
         <v>1056</v>
       </c>
-      <c r="AW99" s="35"/>
-      <c r="AX99" s="35"/>
-      <c r="AY99" s="35"/>
+      <c r="AZ99" s="35"/>
+      <c r="BA99" s="35"/>
+      <c r="BB99" s="35"/>
     </row>
-    <row r="100" spans="1:51" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>922</v>
       </c>
@@ -19281,14 +20151,21 @@
         <v>18</v>
       </c>
       <c r="AU100"/>
-      <c r="AV100" s="9" t="s">
+      <c r="AV100" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW100"/>
+      <c r="AX100" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY100" s="9" t="s">
         <v>1056</v>
       </c>
-      <c r="AW100" s="35"/>
-      <c r="AX100" s="35"/>
-      <c r="AY100" s="35"/>
+      <c r="AZ100" s="35"/>
+      <c r="BA100" s="35"/>
+      <c r="BB100" s="35"/>
     </row>
-    <row r="101" spans="1:51" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>954</v>
       </c>
@@ -19402,14 +20279,21 @@
         <v>18</v>
       </c>
       <c r="AU101"/>
-      <c r="AV101" s="9" t="s">
+      <c r="AV101" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW101"/>
+      <c r="AX101" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY101" s="9" t="s">
         <v>1056</v>
       </c>
-      <c r="AW101" s="35"/>
-      <c r="AX101" s="35"/>
-      <c r="AY101" s="35"/>
+      <c r="AZ101" s="35"/>
+      <c r="BA101" s="35"/>
+      <c r="BB101" s="35"/>
     </row>
-    <row r="102" spans="1:51" ht="90" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>146</v>
       </c>
@@ -19546,20 +20430,29 @@
         <v>18</v>
       </c>
       <c r="AU102"/>
-      <c r="AV102" s="9" t="s">
+      <c r="AV102" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW102" s="40">
+        <v>45728</v>
+      </c>
+      <c r="AX102" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY102" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW102" s="35" t="s">
+      <c r="AZ102" s="35" t="s">
         <v>1099</v>
       </c>
-      <c r="AX102" s="35" t="s">
+      <c r="BA102" s="35" t="s">
         <v>1100</v>
       </c>
-      <c r="AY102" s="35" t="s">
+      <c r="BB102" s="35" t="s">
         <v>1101</v>
       </c>
     </row>
-    <row r="103" spans="1:51" ht="15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>923</v>
       </c>
@@ -19673,14 +20566,21 @@
         <v>18</v>
       </c>
       <c r="AU103"/>
-      <c r="AV103" s="9" t="s">
+      <c r="AV103" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW103"/>
+      <c r="AX103" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY103" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW103" s="35"/>
-      <c r="AX103" s="35"/>
-      <c r="AY103" s="35"/>
+      <c r="AZ103" s="35"/>
+      <c r="BA103" s="35"/>
+      <c r="BB103" s="35"/>
     </row>
-    <row r="104" spans="1:51" ht="15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>924</v>
       </c>
@@ -19794,14 +20694,21 @@
         <v>18</v>
       </c>
       <c r="AU104"/>
-      <c r="AV104" s="9" t="s">
+      <c r="AV104" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW104"/>
+      <c r="AX104" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY104" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW104" s="35"/>
-      <c r="AX104" s="35"/>
-      <c r="AY104" s="35"/>
+      <c r="AZ104" s="35"/>
+      <c r="BA104" s="35"/>
+      <c r="BB104" s="35"/>
     </row>
-    <row r="105" spans="1:51" ht="15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>925</v>
       </c>
@@ -19916,12 +20823,19 @@
         <v>18</v>
       </c>
       <c r="AU105"/>
-      <c r="AV105" s="9" t="s">
+      <c r="AV105" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AW105"/>
+      <c r="AX105" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY105" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AW105" s="35"/>
-      <c r="AX105" s="35"/>
-      <c r="AY105" s="35"/>
+      <c r="AZ105" s="35"/>
+      <c r="BA105" s="35"/>
+      <c r="BB105" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
